--- a/customers_sample.xlsx
+++ b/customers_sample.xlsx
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ramesh Kumar</t>
+          <t>Madhumathi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>+919000666914</t>
+          <t>+916281670029</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,19 +456,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lead_followup</t>
+          <t>marketing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sita Reddy</t>
+          <t>Madhumathi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>+919876543210</t>
+          <t>+916281670029</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,12 +485,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Anil Verma</t>
+          <t>Madhumathi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>+918047491899</t>
+          <t>+916281670029</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
